--- a/data/trans_dic/IP24_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,71</t>
+          <t>1,88; 18,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 16,86</t>
+          <t>1,67; 13,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 10,88</t>
+          <t>3,24; 13,97</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 10,04</t>
+          <t>9,4; 14,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,92</t>
+          <t>5,71; 9,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,32</t>
+          <t>8,1; 11,62</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 17,78</t>
+          <t>15,7; 27,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 25,39</t>
+          <t>9,63; 18,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,43; 20,4</t>
+          <t>13,94; 21,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 10,78</t>
+          <t>11,37; 16,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 15,15</t>
+          <t>7,23; 10,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 12,24</t>
+          <t>9,88; 13,01</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6974</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>722; 6948</t>
+          <t>1048; 10190</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1463; 10298</t>
+          <t>779; 6403</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3022; 12597</t>
+          <t>3321; 14319</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>55442</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56484</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>87562</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24161; 46006</t>
+          <t>44532; 70291</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45015; 71541</t>
+          <t>24551; 41120</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73775; 110101</t>
+          <t>73251; 105001</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>34544</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55386</t>
+          <t>54792</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13424; 26586</t>
+          <t>26337; 45865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27107; 46349</t>
+          <t>14442; 28203</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44608; 67742</t>
+          <t>44279; 67333</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>55847</t>
+          <t>94319</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45001; 71429</t>
+          <t>79290; 113187</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81121; 114773</t>
+          <t>45317; 67697</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130717; 173814</t>
+          <t>130896; 172229</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que hacen entrenamiento deportivo o físico varias veces por semana (tasa de respuesta: 99,43%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,88; 18,27</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,67; 13,69</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3,24; 13,97</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,4; 14,84</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,71; 9,56</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8,1; 11,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15,7; 27,34</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,63; 18,81</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13,94; 21,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11,37; 16,23</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,23; 10,8</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,88; 13,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.07771309209335303</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.0564631737491804</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.06802206613711405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4334</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6974</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.01878923874310836</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01665635028750129</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.03238692077702871</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1048; 10190</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>779; 6403</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3321; 14319</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1827213903538527</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1369371277962879</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1396618223881008</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1170433501238751</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.07464746286866004</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.09686294513358297</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>55442</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>32120</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>87562</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.09401265428569774</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.05705613964102567</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.08103179021811156</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>44532; 70291</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>24551; 41120</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>73251; 105001</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1483916785100807</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.095563070215609</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1161550663578706</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2058948605316451</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1350076108013658</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1724365596244265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>34544</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20248</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>54792</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1569796060719788</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.09629521309574818</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1393506736403431</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>26337; 45865</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14442; 28203</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>44279; 67333</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2733695364285164</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1880514699997838</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2119033657067879</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1352778258670091</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.08772881353119201</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.112763682570976</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>94319</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>55008</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149328</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1137212710526864</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.07227364590020526</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.09884501624284425</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>79290; 113187</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>45317; 67697</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>130896; 172229</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1623384425302957</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1079650330327585</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1300573483962717</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que hacen entrenamiento deportivo o físico varias veces por semana (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4334</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2640</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>6974</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>779</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>3321</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>10190</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6403</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>14319</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>55442</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>32120</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>87562</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>44532</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>24551</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>73251</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>70291</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>41120</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>105001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>34544</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>20248</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>54792</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>26337</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>14442</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>44279</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>45865</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>28203</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>67333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>94319</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>55008</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>149328</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>79290</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>45317</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>130896</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>113187</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>67697</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>172229</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>